--- a/Stock_OneClick/history/scan_result_20260601_091115.xlsx
+++ b/Stock_OneClick/history/scan_result_20260601_091115.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q116"/>
+  <dimension ref="A1:Q115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -638,24 +638,6 @@
       <c r="J3" t="n">
         <v>182.0111</v>
       </c>
-      <c r="K3" t="n">
-        <v/>
-      </c>
-      <c r="L3" t="n">
-        <v/>
-      </c>
-      <c r="M3" t="n">
-        <v/>
-      </c>
-      <c r="N3" t="n">
-        <v/>
-      </c>
-      <c r="O3" t="n">
-        <v/>
-      </c>
-      <c r="P3" t="n">
-        <v/>
-      </c>
       <c r="Q3" t="inlineStr">
         <is>
           <t>D0=181.49; 最新=2026-06-01; 相对D0=0.29%; 本次触发=2026-06-01(正式买入 | 预警买入); 历史重复2次; 重复日期=2026-05-27, 2026-06-01</t>
@@ -707,24 +689,6 @@
       <c r="J4" t="n">
         <v>136.995</v>
       </c>
-      <c r="K4" t="n">
-        <v/>
-      </c>
-      <c r="L4" t="n">
-        <v/>
-      </c>
-      <c r="M4" t="n">
-        <v/>
-      </c>
-      <c r="N4" t="n">
-        <v/>
-      </c>
-      <c r="O4" t="n">
-        <v/>
-      </c>
-      <c r="P4" t="n">
-        <v/>
-      </c>
       <c r="Q4" t="inlineStr">
         <is>
           <t>D0=141.22; 最新=2026-06-01; 相对D0=-2.99%; 本次触发=2026-06-01(正式买入 | 预警买入); 历史重复1次; 重复日期=2026-06-01</t>
@@ -776,27 +740,15 @@
       <c r="J5" s="5" t="n">
         <v>185.275</v>
       </c>
-      <c r="K5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P5" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K5" s="5" t="n"/>
+      <c r="L5" s="5" t="n"/>
+      <c r="M5" s="5" t="n"/>
+      <c r="N5" s="5" t="n"/>
+      <c r="O5" s="5" t="n"/>
+      <c r="P5" s="5" t="n"/>
       <c r="Q5" s="5" t="inlineStr">
         <is>
-          <t>D0=179.36; 最新=2026-06-01; 相对D0=3.30%; 本次触发=2026-06-01(正式买入 | 第一买入点 | 预警买入); 历史重复3次; 重复日期=2026-05-26, 2026-05-28, 2026-06-01</t>
+          <t>D0=179.36; 最新=2026-06-01; 相对D0=3.30%; 本次触发=2026-06-01(正式买入 | 第一观察点 | 预警买入); 历史重复3次; 重复日期=2026-05-26, 2026-05-28, 2026-06-01</t>
         </is>
       </c>
     </row>
@@ -845,24 +797,12 @@
       <c r="J6" s="5" t="n">
         <v>70.755</v>
       </c>
-      <c r="K6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P6" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K6" s="5" t="n"/>
+      <c r="L6" s="5" t="n"/>
+      <c r="M6" s="5" t="n"/>
+      <c r="N6" s="5" t="n"/>
+      <c r="O6" s="5" t="n"/>
+      <c r="P6" s="5" t="n"/>
       <c r="Q6" s="5" t="inlineStr">
         <is>
           <t>D0=73.46; 最新=2026-06-01; 相对D0=-3.68%; 本次触发=2026-06-01(正式买入 | 预警买入); 历史重复1次; 重复日期=2026-06-01</t>
@@ -914,24 +854,12 @@
       <c r="J7" s="5" t="n">
         <v>68.405</v>
       </c>
-      <c r="K7" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L7" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M7" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N7" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O7" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P7" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K7" s="5" t="n"/>
+      <c r="L7" s="5" t="n"/>
+      <c r="M7" s="5" t="n"/>
+      <c r="N7" s="5" t="n"/>
+      <c r="O7" s="5" t="n"/>
+      <c r="P7" s="5" t="n"/>
       <c r="Q7" s="5" t="inlineStr">
         <is>
           <t>D0=68.70; 最新=2026-06-01; 相对D0=-0.43%; 本次触发=2026-06-01(预警买入); 历史重复1次; 重复日期=2026-06-01</t>
@@ -983,24 +911,12 @@
       <c r="J8" s="5" t="n">
         <v>18.44</v>
       </c>
-      <c r="K8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P8" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K8" s="5" t="n"/>
+      <c r="L8" s="5" t="n"/>
+      <c r="M8" s="5" t="n"/>
+      <c r="N8" s="5" t="n"/>
+      <c r="O8" s="5" t="n"/>
+      <c r="P8" s="5" t="n"/>
       <c r="Q8" s="5" t="inlineStr">
         <is>
           <t>D0=18.40; 最新=2026-06-01; 相对D0=0.22%; 本次触发=2026-06-01(预警买入); 历史重复1次; 重复日期=2026-06-01</t>
@@ -1052,24 +968,6 @@
       <c r="J9" t="n">
         <v>39.4</v>
       </c>
-      <c r="K9" t="n">
-        <v/>
-      </c>
-      <c r="L9" t="n">
-        <v/>
-      </c>
-      <c r="M9" t="n">
-        <v/>
-      </c>
-      <c r="N9" t="n">
-        <v/>
-      </c>
-      <c r="O9" t="n">
-        <v/>
-      </c>
-      <c r="P9" t="n">
-        <v/>
-      </c>
       <c r="Q9" t="inlineStr">
         <is>
           <t>D0=41.35; 最新=2026-06-01; 相对D0=-4.72%; 本次触发=2026-06-01(正式买入 | 预警买入); 历史重复1次; 重复日期=2026-06-01</t>
@@ -1121,24 +1019,12 @@
       <c r="J10" s="5" t="n">
         <v>220.255</v>
       </c>
-      <c r="K10" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L10" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M10" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N10" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O10" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P10" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K10" s="5" t="n"/>
+      <c r="L10" s="5" t="n"/>
+      <c r="M10" s="5" t="n"/>
+      <c r="N10" s="5" t="n"/>
+      <c r="O10" s="5" t="n"/>
+      <c r="P10" s="5" t="n"/>
       <c r="Q10" s="5" t="inlineStr">
         <is>
           <t>D0=211.14; 最新=2026-06-01; 相对D0=4.32%; 本次触发=2026-06-01(正式买入 | 预警买入); 历史重复1次; 重复日期=2026-06-01</t>
@@ -1190,24 +1076,6 @@
       <c r="J11" t="n">
         <v>14.68</v>
       </c>
-      <c r="K11" t="n">
-        <v/>
-      </c>
-      <c r="L11" t="n">
-        <v/>
-      </c>
-      <c r="M11" t="n">
-        <v/>
-      </c>
-      <c r="N11" t="n">
-        <v/>
-      </c>
-      <c r="O11" t="n">
-        <v/>
-      </c>
-      <c r="P11" t="n">
-        <v/>
-      </c>
       <c r="Q11" t="inlineStr">
         <is>
           <t>D0=14.68; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(预警买入)</t>
@@ -1259,24 +1127,6 @@
       <c r="J12" t="n">
         <v>116.95</v>
       </c>
-      <c r="K12" t="n">
-        <v/>
-      </c>
-      <c r="L12" t="n">
-        <v/>
-      </c>
-      <c r="M12" t="n">
-        <v/>
-      </c>
-      <c r="N12" t="n">
-        <v/>
-      </c>
-      <c r="O12" t="n">
-        <v/>
-      </c>
-      <c r="P12" t="n">
-        <v/>
-      </c>
       <c r="Q12" t="inlineStr">
         <is>
           <t>D0=116.95; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(预警买入)</t>
@@ -1328,24 +1178,6 @@
       <c r="J13" t="n">
         <v>186.6601</v>
       </c>
-      <c r="K13" t="n">
-        <v/>
-      </c>
-      <c r="L13" t="n">
-        <v/>
-      </c>
-      <c r="M13" t="n">
-        <v/>
-      </c>
-      <c r="N13" t="n">
-        <v/>
-      </c>
-      <c r="O13" t="n">
-        <v/>
-      </c>
-      <c r="P13" t="n">
-        <v/>
-      </c>
       <c r="Q13" t="inlineStr">
         <is>
           <t>D0=186.66; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式买入 | 预警买入)</t>
@@ -1366,9 +1198,6 @@
           <t>DXY</t>
         </is>
       </c>
-      <c r="D14" t="n">
-        <v/>
-      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>98 TradingView导入</t>
@@ -1395,24 +1224,6 @@
       <c r="J14" t="n">
         <v>99.23699999999999</v>
       </c>
-      <c r="K14" t="n">
-        <v/>
-      </c>
-      <c r="L14" t="n">
-        <v/>
-      </c>
-      <c r="M14" t="n">
-        <v/>
-      </c>
-      <c r="N14" t="n">
-        <v/>
-      </c>
-      <c r="O14" t="n">
-        <v/>
-      </c>
-      <c r="P14" t="n">
-        <v/>
-      </c>
       <c r="Q14" t="inlineStr">
         <is>
           <t>D0=99.24; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式买入 | 预警买入)</t>
@@ -1464,24 +1275,6 @@
       <c r="J15" t="n">
         <v>8.675000000000001</v>
       </c>
-      <c r="K15" t="n">
-        <v/>
-      </c>
-      <c r="L15" t="n">
-        <v/>
-      </c>
-      <c r="M15" t="n">
-        <v/>
-      </c>
-      <c r="N15" t="n">
-        <v/>
-      </c>
-      <c r="O15" t="n">
-        <v/>
-      </c>
-      <c r="P15" t="n">
-        <v/>
-      </c>
       <c r="Q15" t="inlineStr">
         <is>
           <t>D0=8.68; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(预警买入)</t>
@@ -1533,24 +1326,6 @@
       <c r="J16" t="n">
         <v>26.175</v>
       </c>
-      <c r="K16" t="n">
-        <v/>
-      </c>
-      <c r="L16" t="n">
-        <v/>
-      </c>
-      <c r="M16" t="n">
-        <v/>
-      </c>
-      <c r="N16" t="n">
-        <v/>
-      </c>
-      <c r="O16" t="n">
-        <v/>
-      </c>
-      <c r="P16" t="n">
-        <v/>
-      </c>
       <c r="Q16" t="inlineStr">
         <is>
           <t>D0=26.18; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式买入 | 预警买入)</t>
@@ -1602,24 +1377,6 @@
       <c r="J17" t="n">
         <v>887.39</v>
       </c>
-      <c r="K17" t="n">
-        <v/>
-      </c>
-      <c r="L17" t="n">
-        <v/>
-      </c>
-      <c r="M17" t="n">
-        <v/>
-      </c>
-      <c r="N17" t="n">
-        <v/>
-      </c>
-      <c r="O17" t="n">
-        <v/>
-      </c>
-      <c r="P17" t="n">
-        <v/>
-      </c>
       <c r="Q17" t="inlineStr">
         <is>
           <t>D0=887.39; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(预警买入)</t>
@@ -1671,24 +1428,6 @@
       <c r="J18" t="n">
         <v>11.65</v>
       </c>
-      <c r="K18" t="n">
-        <v/>
-      </c>
-      <c r="L18" t="n">
-        <v/>
-      </c>
-      <c r="M18" t="n">
-        <v/>
-      </c>
-      <c r="N18" t="n">
-        <v/>
-      </c>
-      <c r="O18" t="n">
-        <v/>
-      </c>
-      <c r="P18" t="n">
-        <v/>
-      </c>
       <c r="Q18" t="inlineStr">
         <is>
           <t>D0=11.65; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(预警买入)</t>
@@ -1740,24 +1479,6 @@
       <c r="J19" t="n">
         <v>59.47</v>
       </c>
-      <c r="K19" t="n">
-        <v/>
-      </c>
-      <c r="L19" t="n">
-        <v/>
-      </c>
-      <c r="M19" t="n">
-        <v/>
-      </c>
-      <c r="N19" t="n">
-        <v/>
-      </c>
-      <c r="O19" t="n">
-        <v/>
-      </c>
-      <c r="P19" t="n">
-        <v/>
-      </c>
       <c r="Q19" t="inlineStr">
         <is>
           <t>D0=59.47; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式买入 | 预警买入)</t>
@@ -1809,24 +1530,6 @@
       <c r="J20" t="n">
         <v>13.8895</v>
       </c>
-      <c r="K20" t="n">
-        <v/>
-      </c>
-      <c r="L20" t="n">
-        <v/>
-      </c>
-      <c r="M20" t="n">
-        <v/>
-      </c>
-      <c r="N20" t="n">
-        <v/>
-      </c>
-      <c r="O20" t="n">
-        <v/>
-      </c>
-      <c r="P20" t="n">
-        <v/>
-      </c>
       <c r="Q20" t="inlineStr">
         <is>
           <t>D0=13.89; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式买入 | 预警买入)</t>
@@ -1847,9 +1550,6 @@
           <t>VIX</t>
         </is>
       </c>
-      <c r="D21" t="n">
-        <v/>
-      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>98 TradingView导入</t>
@@ -1876,24 +1576,6 @@
       <c r="J21" t="n">
         <v>16</v>
       </c>
-      <c r="K21" t="n">
-        <v/>
-      </c>
-      <c r="L21" t="n">
-        <v/>
-      </c>
-      <c r="M21" t="n">
-        <v/>
-      </c>
-      <c r="N21" t="n">
-        <v/>
-      </c>
-      <c r="O21" t="n">
-        <v/>
-      </c>
-      <c r="P21" t="n">
-        <v/>
-      </c>
       <c r="Q21" t="inlineStr">
         <is>
           <t>D0=16.00; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(预警买入)</t>
@@ -1945,24 +1627,12 @@
       <c r="J22" s="5" t="n">
         <v>154.305</v>
       </c>
-      <c r="K22" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L22" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M22" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N22" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O22" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P22" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K22" s="5" t="n"/>
+      <c r="L22" s="5" t="n"/>
+      <c r="M22" s="5" t="n"/>
+      <c r="N22" s="5" t="n"/>
+      <c r="O22" s="5" t="n"/>
+      <c r="P22" s="5" t="n"/>
       <c r="Q22" s="5" t="inlineStr">
         <is>
           <t>D0=154.31; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式买入 | 预警买入)</t>
@@ -2014,24 +1684,12 @@
       <c r="J23" s="5" t="n">
         <v>186.84</v>
       </c>
-      <c r="K23" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L23" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M23" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N23" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O23" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P23" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K23" s="5" t="n"/>
+      <c r="L23" s="5" t="n"/>
+      <c r="M23" s="5" t="n"/>
+      <c r="N23" s="5" t="n"/>
+      <c r="O23" s="5" t="n"/>
+      <c r="P23" s="5" t="n"/>
       <c r="Q23" s="5" t="inlineStr">
         <is>
           <t>D0=202.91; 最新=2026-06-01; 相对D0=-7.92%; 历史重复1次; 重复日期=2026-05-26</t>
@@ -2083,24 +1741,12 @@
       <c r="J24" s="5" t="n">
         <v>164.25</v>
       </c>
-      <c r="K24" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L24" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M24" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N24" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O24" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P24" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K24" s="5" t="n"/>
+      <c r="L24" s="5" t="n"/>
+      <c r="M24" s="5" t="n"/>
+      <c r="N24" s="5" t="n"/>
+      <c r="O24" s="5" t="n"/>
+      <c r="P24" s="5" t="n"/>
       <c r="Q24" s="5" t="inlineStr">
         <is>
           <t>D0=167.37; 最新=2026-06-01; 相对D0=-1.86%; 历史重复2次; 重复日期=2026-05-26, 2026-05-29</t>
@@ -2152,24 +1798,12 @@
       <c r="J25" s="5" t="n">
         <v>53.39</v>
       </c>
-      <c r="K25" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L25" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M25" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N25" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O25" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P25" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K25" s="5" t="n"/>
+      <c r="L25" s="5" t="n"/>
+      <c r="M25" s="5" t="n"/>
+      <c r="N25" s="5" t="n"/>
+      <c r="O25" s="5" t="n"/>
+      <c r="P25" s="5" t="n"/>
       <c r="Q25" s="5" t="inlineStr">
         <is>
           <t>D0=46.53; 最新=2026-06-01; 相对D0=14.74%</t>
@@ -2221,24 +1855,6 @@
       <c r="J26" t="n">
         <v>16.785</v>
       </c>
-      <c r="K26" t="n">
-        <v/>
-      </c>
-      <c r="L26" t="n">
-        <v/>
-      </c>
-      <c r="M26" t="n">
-        <v/>
-      </c>
-      <c r="N26" t="n">
-        <v/>
-      </c>
-      <c r="O26" t="n">
-        <v/>
-      </c>
-      <c r="P26" t="n">
-        <v/>
-      </c>
       <c r="Q26" t="inlineStr">
         <is>
           <t>D0=16.12; 最新=2026-06-01; 相对D0=4.13%; 历史重复1次; 重复日期=2026-05-27</t>
@@ -2290,24 +1906,12 @@
       <c r="J27" s="5" t="n">
         <v>210.01</v>
       </c>
-      <c r="K27" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L27" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M27" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N27" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O27" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P27" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K27" s="5" t="n"/>
+      <c r="L27" s="5" t="n"/>
+      <c r="M27" s="5" t="n"/>
+      <c r="N27" s="5" t="n"/>
+      <c r="O27" s="5" t="n"/>
+      <c r="P27" s="5" t="n"/>
       <c r="Q27" s="5" t="inlineStr">
         <is>
           <t>D0=180.07; 最新=2026-06-01; 相对D0=16.63%; 历史重复2次; 重复日期=2026-05-28, 2026-05-29</t>
@@ -2359,24 +1963,12 @@
       <c r="J28" s="5" t="n">
         <v>47.58</v>
       </c>
-      <c r="K28" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L28" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M28" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N28" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O28" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P28" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K28" s="5" t="n"/>
+      <c r="L28" s="5" t="n"/>
+      <c r="M28" s="5" t="n"/>
+      <c r="N28" s="5" t="n"/>
+      <c r="O28" s="5" t="n"/>
+      <c r="P28" s="5" t="n"/>
       <c r="Q28" s="5" t="inlineStr">
         <is>
           <t>D0=48.12; 最新=2026-06-01; 相对D0=-1.12%; 历史重复2次; 重复日期=2026-05-26, 2026-05-29</t>
@@ -2428,24 +2020,6 @@
       <c r="J29" t="n">
         <v>399.69</v>
       </c>
-      <c r="K29" t="n">
-        <v/>
-      </c>
-      <c r="L29" t="n">
-        <v/>
-      </c>
-      <c r="M29" t="n">
-        <v/>
-      </c>
-      <c r="N29" t="n">
-        <v/>
-      </c>
-      <c r="O29" t="n">
-        <v/>
-      </c>
-      <c r="P29" t="n">
-        <v/>
-      </c>
       <c r="Q29" t="inlineStr">
         <is>
           <t>D0=391.35; 最新=2026-06-01; 相对D0=2.13%; 历史重复1次; 重复日期=2026-05-26</t>
@@ -2497,24 +2071,6 @@
       <c r="J30" t="n">
         <v>953.85</v>
       </c>
-      <c r="K30" t="n">
-        <v/>
-      </c>
-      <c r="L30" t="n">
-        <v/>
-      </c>
-      <c r="M30" t="n">
-        <v/>
-      </c>
-      <c r="N30" t="n">
-        <v/>
-      </c>
-      <c r="O30" t="n">
-        <v/>
-      </c>
-      <c r="P30" t="n">
-        <v/>
-      </c>
       <c r="Q30" t="inlineStr">
         <is>
           <t>D0=1038.74; 最新=2026-06-01; 相对D0=-8.17%; 历史重复1次; 重复日期=2026-05-26</t>
@@ -2566,24 +2122,12 @@
       <c r="J31" s="5" t="n">
         <v>395.52</v>
       </c>
-      <c r="K31" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L31" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M31" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N31" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O31" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P31" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K31" s="5" t="n"/>
+      <c r="L31" s="5" t="n"/>
+      <c r="M31" s="5" t="n"/>
+      <c r="N31" s="5" t="n"/>
+      <c r="O31" s="5" t="n"/>
+      <c r="P31" s="5" t="n"/>
       <c r="Q31" s="5" t="inlineStr">
         <is>
           <t>D0=326.13; 最新=2026-06-01; 相对D0=21.28%; 历史重复1次; 重复日期=2026-05-28</t>
@@ -2635,24 +2179,6 @@
       <c r="J32" t="n">
         <v>23.315</v>
       </c>
-      <c r="K32" t="n">
-        <v/>
-      </c>
-      <c r="L32" t="n">
-        <v/>
-      </c>
-      <c r="M32" t="n">
-        <v/>
-      </c>
-      <c r="N32" t="n">
-        <v/>
-      </c>
-      <c r="O32" t="n">
-        <v/>
-      </c>
-      <c r="P32" t="n">
-        <v/>
-      </c>
       <c r="Q32" t="inlineStr">
         <is>
           <t>D0=22.51; 最新=2026-06-01; 相对D0=3.58%; 历史重复1次; 重复日期=2026-05-26</t>
@@ -2704,24 +2230,6 @@
       <c r="J33" t="n">
         <v>250.03</v>
       </c>
-      <c r="K33" t="n">
-        <v/>
-      </c>
-      <c r="L33" t="n">
-        <v/>
-      </c>
-      <c r="M33" t="n">
-        <v/>
-      </c>
-      <c r="N33" t="n">
-        <v/>
-      </c>
-      <c r="O33" t="n">
-        <v/>
-      </c>
-      <c r="P33" t="n">
-        <v/>
-      </c>
       <c r="Q33" t="inlineStr">
         <is>
           <t>D0=232.00; 最新=2026-06-01; 相对D0=7.77%</t>
@@ -2773,24 +2281,6 @@
       <c r="J34" t="n">
         <v>144.06</v>
       </c>
-      <c r="K34" t="n">
-        <v/>
-      </c>
-      <c r="L34" t="n">
-        <v/>
-      </c>
-      <c r="M34" t="n">
-        <v/>
-      </c>
-      <c r="N34" t="n">
-        <v/>
-      </c>
-      <c r="O34" t="n">
-        <v/>
-      </c>
-      <c r="P34" t="n">
-        <v/>
-      </c>
       <c r="Q34" t="inlineStr">
         <is>
           <t>D0=130.50; 最新=2026-06-01; 相对D0=10.39%</t>
@@ -2842,24 +2332,12 @@
       <c r="J35" s="5" t="n">
         <v>253.56</v>
       </c>
-      <c r="K35" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L35" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M35" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N35" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O35" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P35" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K35" s="5" t="n"/>
+      <c r="L35" s="5" t="n"/>
+      <c r="M35" s="5" t="n"/>
+      <c r="N35" s="5" t="n"/>
+      <c r="O35" s="5" t="n"/>
+      <c r="P35" s="5" t="n"/>
       <c r="Q35" s="5" t="inlineStr">
         <is>
           <t>D0=262.25; 最新=2026-06-01; 相对D0=-3.31%; 历史重复2次; 重复日期=2026-05-26, 2026-05-27</t>
@@ -2911,24 +2389,12 @@
       <c r="J36" s="5" t="n">
         <v>115.99</v>
       </c>
-      <c r="K36" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L36" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M36" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N36" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O36" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P36" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K36" s="5" t="n"/>
+      <c r="L36" s="5" t="n"/>
+      <c r="M36" s="5" t="n"/>
+      <c r="N36" s="5" t="n"/>
+      <c r="O36" s="5" t="n"/>
+      <c r="P36" s="5" t="n"/>
       <c r="Q36" s="5" t="inlineStr">
         <is>
           <t>D0=85.42; 最新=2026-06-01; 相对D0=35.79%; 历史重复1次; 重复日期=2026-05-27</t>
@@ -2980,24 +2446,12 @@
       <c r="J37" s="5" t="n">
         <v>419.67</v>
       </c>
-      <c r="K37" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L37" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M37" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N37" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O37" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P37" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K37" s="5" t="n"/>
+      <c r="L37" s="5" t="n"/>
+      <c r="M37" s="5" t="n"/>
+      <c r="N37" s="5" t="n"/>
+      <c r="O37" s="5" t="n"/>
+      <c r="P37" s="5" t="n"/>
       <c r="Q37" s="5" t="inlineStr">
         <is>
           <t>D0=426.01; 最新=2026-06-01; 相对D0=-1.49%</t>
@@ -3049,24 +2503,12 @@
       <c r="J38" s="5" t="n">
         <v>13.635</v>
       </c>
-      <c r="K38" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L38" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M38" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N38" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O38" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P38" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K38" s="5" t="n"/>
+      <c r="L38" s="5" t="n"/>
+      <c r="M38" s="5" t="n"/>
+      <c r="N38" s="5" t="n"/>
+      <c r="O38" s="5" t="n"/>
+      <c r="P38" s="5" t="n"/>
       <c r="Q38" s="5" t="inlineStr">
         <is>
           <t>D0=13.02; 最新=2026-06-01; 相对D0=4.72%; 历史重复2次; 重复日期=2026-05-26, 2026-05-29</t>
@@ -3118,24 +2560,6 @@
       <c r="J39" t="n">
         <v>462.355</v>
       </c>
-      <c r="K39" t="n">
-        <v/>
-      </c>
-      <c r="L39" t="n">
-        <v/>
-      </c>
-      <c r="M39" t="n">
-        <v/>
-      </c>
-      <c r="N39" t="n">
-        <v/>
-      </c>
-      <c r="O39" t="n">
-        <v/>
-      </c>
-      <c r="P39" t="n">
-        <v/>
-      </c>
       <c r="Q39" t="inlineStr">
         <is>
           <t>D0=422.01; 最新=2026-06-01; 相对D0=9.56%</t>
@@ -3187,24 +2611,6 @@
       <c r="J40" t="n">
         <v>89.98999999999999</v>
       </c>
-      <c r="K40" t="n">
-        <v/>
-      </c>
-      <c r="L40" t="n">
-        <v/>
-      </c>
-      <c r="M40" t="n">
-        <v/>
-      </c>
-      <c r="N40" t="n">
-        <v/>
-      </c>
-      <c r="O40" t="n">
-        <v/>
-      </c>
-      <c r="P40" t="n">
-        <v/>
-      </c>
       <c r="Q40" t="inlineStr">
         <is>
           <t>D0=86.49; 最新=2026-06-01; 相对D0=4.05%</t>
@@ -3256,24 +2662,12 @@
       <c r="J41" s="5" t="n">
         <v>111.25</v>
       </c>
-      <c r="K41" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L41" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M41" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N41" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O41" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P41" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K41" s="5" t="n"/>
+      <c r="L41" s="5" t="n"/>
+      <c r="M41" s="5" t="n"/>
+      <c r="N41" s="5" t="n"/>
+      <c r="O41" s="5" t="n"/>
+      <c r="P41" s="5" t="n"/>
       <c r="Q41" s="5" t="inlineStr">
         <is>
           <t>D0=108.17; 最新=2026-06-01; 相对D0=2.85%; 历史重复1次; 重复日期=2026-05-28</t>
@@ -3325,24 +2719,6 @@
       <c r="J42" t="n">
         <v>122.815</v>
       </c>
-      <c r="K42" t="n">
-        <v/>
-      </c>
-      <c r="L42" t="n">
-        <v/>
-      </c>
-      <c r="M42" t="n">
-        <v/>
-      </c>
-      <c r="N42" t="n">
-        <v/>
-      </c>
-      <c r="O42" t="n">
-        <v/>
-      </c>
-      <c r="P42" t="n">
-        <v/>
-      </c>
       <c r="Q42" t="inlineStr">
         <is>
           <t>D0=105.89; 最新=2026-06-01; 相对D0=15.98%; 历史重复1次; 重复日期=2026-05-28</t>
@@ -3394,24 +2770,6 @@
       <c r="J43" t="n">
         <v>86.17</v>
       </c>
-      <c r="K43" t="n">
-        <v/>
-      </c>
-      <c r="L43" t="n">
-        <v/>
-      </c>
-      <c r="M43" t="n">
-        <v/>
-      </c>
-      <c r="N43" t="n">
-        <v/>
-      </c>
-      <c r="O43" t="n">
-        <v/>
-      </c>
-      <c r="P43" t="n">
-        <v/>
-      </c>
       <c r="Q43" t="inlineStr">
         <is>
           <t>D0=88.50; 最新=2026-06-01; 相对D0=-2.63%; 历史重复2次; 重复日期=2026-05-28, 2026-05-29</t>
@@ -3463,24 +2821,6 @@
       <c r="J44" t="n">
         <v>144.77</v>
       </c>
-      <c r="K44" t="n">
-        <v/>
-      </c>
-      <c r="L44" t="n">
-        <v/>
-      </c>
-      <c r="M44" t="n">
-        <v/>
-      </c>
-      <c r="N44" t="n">
-        <v/>
-      </c>
-      <c r="O44" t="n">
-        <v/>
-      </c>
-      <c r="P44" t="n">
-        <v/>
-      </c>
       <c r="Q44" t="inlineStr">
         <is>
           <t>D0=158.34; 最新=2026-06-01; 相对D0=-8.57%; 历史重复2次; 重复日期=2026-05-28, 2026-05-29</t>
@@ -3532,24 +2872,12 @@
       <c r="J45" s="5" t="n">
         <v>375.15</v>
       </c>
-      <c r="K45" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L45" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M45" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N45" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O45" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P45" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K45" s="5" t="n"/>
+      <c r="L45" s="5" t="n"/>
+      <c r="M45" s="5" t="n"/>
+      <c r="N45" s="5" t="n"/>
+      <c r="O45" s="5" t="n"/>
+      <c r="P45" s="5" t="n"/>
       <c r="Q45" s="5" t="inlineStr">
         <is>
           <t>D0=388.88; 最新=2026-06-01; 相对D0=-3.53%; 历史重复1次; 重复日期=2026-05-28</t>
@@ -3601,24 +2929,12 @@
       <c r="J46" s="5" t="n">
         <v>613.0377</v>
       </c>
-      <c r="K46" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L46" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M46" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N46" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O46" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P46" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K46" s="5" t="n"/>
+      <c r="L46" s="5" t="n"/>
+      <c r="M46" s="5" t="n"/>
+      <c r="N46" s="5" t="n"/>
+      <c r="O46" s="5" t="n"/>
+      <c r="P46" s="5" t="n"/>
       <c r="Q46" s="5" t="inlineStr">
         <is>
           <t>D0=612.34; 最新=2026-06-01; 相对D0=0.11%</t>
@@ -3670,24 +2986,6 @@
       <c r="J47" t="n">
         <v>107.91</v>
       </c>
-      <c r="K47" t="n">
-        <v/>
-      </c>
-      <c r="L47" t="n">
-        <v/>
-      </c>
-      <c r="M47" t="n">
-        <v/>
-      </c>
-      <c r="N47" t="n">
-        <v/>
-      </c>
-      <c r="O47" t="n">
-        <v/>
-      </c>
-      <c r="P47" t="n">
-        <v/>
-      </c>
       <c r="Q47" t="inlineStr">
         <is>
           <t>D0=106.94; 最新=2026-06-01; 相对D0=0.91%</t>
@@ -3739,24 +3037,12 @@
       <c r="J48" s="5" t="n">
         <v>13.125</v>
       </c>
-      <c r="K48" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L48" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M48" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N48" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O48" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P48" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K48" s="5" t="n"/>
+      <c r="L48" s="5" t="n"/>
+      <c r="M48" s="5" t="n"/>
+      <c r="N48" s="5" t="n"/>
+      <c r="O48" s="5" t="n"/>
+      <c r="P48" s="5" t="n"/>
       <c r="Q48" s="5" t="inlineStr">
         <is>
           <t>D0=12.22; 最新=2026-06-01; 相对D0=7.41%</t>
@@ -3808,24 +3094,6 @@
       <c r="J49" t="n">
         <v>84.8</v>
       </c>
-      <c r="K49" t="n">
-        <v/>
-      </c>
-      <c r="L49" t="n">
-        <v/>
-      </c>
-      <c r="M49" t="n">
-        <v/>
-      </c>
-      <c r="N49" t="n">
-        <v/>
-      </c>
-      <c r="O49" t="n">
-        <v/>
-      </c>
-      <c r="P49" t="n">
-        <v/>
-      </c>
       <c r="Q49" t="inlineStr">
         <is>
           <t>D0=84.64; 最新=2026-06-01; 相对D0=0.19%</t>
@@ -3877,24 +3145,6 @@
       <c r="J50" t="n">
         <v>319.88</v>
       </c>
-      <c r="K50" t="n">
-        <v/>
-      </c>
-      <c r="L50" t="n">
-        <v/>
-      </c>
-      <c r="M50" t="n">
-        <v/>
-      </c>
-      <c r="N50" t="n">
-        <v/>
-      </c>
-      <c r="O50" t="n">
-        <v/>
-      </c>
-      <c r="P50" t="n">
-        <v/>
-      </c>
       <c r="Q50" t="inlineStr">
         <is>
           <t>D0=323.91; 最新=2026-06-01; 相对D0=-1.24%</t>
@@ -3946,24 +3196,12 @@
       <c r="J51" s="5" t="n">
         <v>262.9026</v>
       </c>
-      <c r="K51" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L51" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M51" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N51" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O51" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P51" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K51" s="5" t="n"/>
+      <c r="L51" s="5" t="n"/>
+      <c r="M51" s="5" t="n"/>
+      <c r="N51" s="5" t="n"/>
+      <c r="O51" s="5" t="n"/>
+      <c r="P51" s="5" t="n"/>
       <c r="Q51" s="5" t="inlineStr">
         <is>
           <t>D0=271.85; 最新=2026-06-01; 相对D0=-3.29%</t>
@@ -4015,24 +3253,6 @@
       <c r="J52" t="n">
         <v>90.41</v>
       </c>
-      <c r="K52" t="n">
-        <v/>
-      </c>
-      <c r="L52" t="n">
-        <v/>
-      </c>
-      <c r="M52" t="n">
-        <v/>
-      </c>
-      <c r="N52" t="n">
-        <v/>
-      </c>
-      <c r="O52" t="n">
-        <v/>
-      </c>
-      <c r="P52" t="n">
-        <v/>
-      </c>
       <c r="Q52" t="inlineStr">
         <is>
           <t>D0=90.87; 最新=2026-06-01; 相对D0=-0.51%; 历史重复1次; 重复日期=2026-05-28</t>
@@ -4084,24 +3304,12 @@
       <c r="J53" s="5" t="n">
         <v>136.26</v>
       </c>
-      <c r="K53" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L53" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M53" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N53" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O53" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P53" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K53" s="5" t="n"/>
+      <c r="L53" s="5" t="n"/>
+      <c r="M53" s="5" t="n"/>
+      <c r="N53" s="5" t="n"/>
+      <c r="O53" s="5" t="n"/>
+      <c r="P53" s="5" t="n"/>
       <c r="Q53" s="5" t="inlineStr">
         <is>
           <t>D0=102.12; 最新=2026-06-01; 相对D0=33.43%</t>
@@ -4153,24 +3361,6 @@
       <c r="J54" t="n">
         <v>242.525</v>
       </c>
-      <c r="K54" t="n">
-        <v/>
-      </c>
-      <c r="L54" t="n">
-        <v/>
-      </c>
-      <c r="M54" t="n">
-        <v/>
-      </c>
-      <c r="N54" t="n">
-        <v/>
-      </c>
-      <c r="O54" t="n">
-        <v/>
-      </c>
-      <c r="P54" t="n">
-        <v/>
-      </c>
       <c r="Q54" t="inlineStr">
         <is>
           <t>D0=190.96; 最新=2026-06-01; 相对D0=27.00%</t>
@@ -4222,24 +3412,6 @@
       <c r="J55" t="n">
         <v>274.71</v>
       </c>
-      <c r="K55" t="n">
-        <v/>
-      </c>
-      <c r="L55" t="n">
-        <v/>
-      </c>
-      <c r="M55" t="n">
-        <v/>
-      </c>
-      <c r="N55" t="n">
-        <v/>
-      </c>
-      <c r="O55" t="n">
-        <v/>
-      </c>
-      <c r="P55" t="n">
-        <v/>
-      </c>
       <c r="Q55" t="inlineStr">
         <is>
           <t>D0=290.01; 最新=2026-06-01; 相对D0=-5.28%</t>
@@ -4291,24 +3463,12 @@
       <c r="J56" s="5" t="n">
         <v>762.4400000000001</v>
       </c>
-      <c r="K56" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L56" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M56" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N56" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O56" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P56" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K56" s="5" t="n"/>
+      <c r="L56" s="5" t="n"/>
+      <c r="M56" s="5" t="n"/>
+      <c r="N56" s="5" t="n"/>
+      <c r="O56" s="5" t="n"/>
+      <c r="P56" s="5" t="n"/>
       <c r="Q56" s="5" t="inlineStr">
         <is>
           <t>D0=671.00; 最新=2026-06-01; 相对D0=13.63%</t>
@@ -4360,24 +3520,6 @@
       <c r="J57" t="n">
         <v>65.2002</v>
       </c>
-      <c r="K57" t="n">
-        <v/>
-      </c>
-      <c r="L57" t="n">
-        <v/>
-      </c>
-      <c r="M57" t="n">
-        <v/>
-      </c>
-      <c r="N57" t="n">
-        <v/>
-      </c>
-      <c r="O57" t="n">
-        <v/>
-      </c>
-      <c r="P57" t="n">
-        <v/>
-      </c>
       <c r="Q57" t="inlineStr">
         <is>
           <t>D0=67.38; 最新=2026-06-01; 相对D0=-3.24%</t>
@@ -4429,24 +3571,6 @@
       <c r="J58" t="n">
         <v>1059.67</v>
       </c>
-      <c r="K58" t="n">
-        <v/>
-      </c>
-      <c r="L58" t="n">
-        <v/>
-      </c>
-      <c r="M58" t="n">
-        <v/>
-      </c>
-      <c r="N58" t="n">
-        <v/>
-      </c>
-      <c r="O58" t="n">
-        <v/>
-      </c>
-      <c r="P58" t="n">
-        <v/>
-      </c>
       <c r="Q58" t="inlineStr">
         <is>
           <t>D0=1069.44; 最新=2026-06-01; 相对D0=-0.91%</t>
@@ -4498,24 +3622,12 @@
       <c r="J59" s="5" t="n">
         <v>144.605</v>
       </c>
-      <c r="K59" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L59" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M59" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N59" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O59" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P59" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K59" s="5" t="n"/>
+      <c r="L59" s="5" t="n"/>
+      <c r="M59" s="5" t="n"/>
+      <c r="N59" s="5" t="n"/>
+      <c r="O59" s="5" t="n"/>
+      <c r="P59" s="5" t="n"/>
       <c r="Q59" s="5" t="inlineStr">
         <is>
           <t>D0=129.70; 最新=2026-06-01; 相对D0=11.49%</t>
@@ -4567,24 +3679,12 @@
       <c r="J60" s="5" t="n">
         <v>106.76</v>
       </c>
-      <c r="K60" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L60" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M60" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N60" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O60" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P60" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K60" s="5" t="n"/>
+      <c r="L60" s="5" t="n"/>
+      <c r="M60" s="5" t="n"/>
+      <c r="N60" s="5" t="n"/>
+      <c r="O60" s="5" t="n"/>
+      <c r="P60" s="5" t="n"/>
       <c r="Q60" s="5" t="inlineStr">
         <is>
           <t>D0=95.68; 最新=2026-06-01; 相对D0=11.58%</t>
@@ -4636,24 +3736,12 @@
       <c r="J61" s="5" t="n">
         <v>459.88</v>
       </c>
-      <c r="K61" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L61" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M61" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N61" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O61" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P61" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K61" s="5" t="n"/>
+      <c r="L61" s="5" t="n"/>
+      <c r="M61" s="5" t="n"/>
+      <c r="N61" s="5" t="n"/>
+      <c r="O61" s="5" t="n"/>
+      <c r="P61" s="5" t="n"/>
       <c r="Q61" s="5" t="inlineStr">
         <is>
           <t>D0=426.99; 最新=2026-06-01; 相对D0=7.70%</t>
@@ -4705,24 +3793,6 @@
       <c r="J62" t="n">
         <v>271.98</v>
       </c>
-      <c r="K62" t="n">
-        <v/>
-      </c>
-      <c r="L62" t="n">
-        <v/>
-      </c>
-      <c r="M62" t="n">
-        <v/>
-      </c>
-      <c r="N62" t="n">
-        <v/>
-      </c>
-      <c r="O62" t="n">
-        <v/>
-      </c>
-      <c r="P62" t="n">
-        <v/>
-      </c>
       <c r="Q62" t="inlineStr">
         <is>
           <t>D0=226.34; 最新=2026-06-01; 相对D0=20.16%</t>
@@ -4774,24 +3844,12 @@
       <c r="J63" s="5" t="n">
         <v>139.19</v>
       </c>
-      <c r="K63" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L63" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M63" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N63" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O63" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P63" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K63" s="5" t="n"/>
+      <c r="L63" s="5" t="n"/>
+      <c r="M63" s="5" t="n"/>
+      <c r="N63" s="5" t="n"/>
+      <c r="O63" s="5" t="n"/>
+      <c r="P63" s="5" t="n"/>
       <c r="Q63" s="5" t="inlineStr">
         <is>
           <t>D0=94.72; 最新=2026-06-01; 相对D0=46.95%</t>
@@ -4843,24 +3901,12 @@
       <c r="J64" s="5" t="n">
         <v>294.35</v>
       </c>
-      <c r="K64" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L64" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M64" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N64" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O64" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P64" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K64" s="5" t="n"/>
+      <c r="L64" s="5" t="n"/>
+      <c r="M64" s="5" t="n"/>
+      <c r="N64" s="5" t="n"/>
+      <c r="O64" s="5" t="n"/>
+      <c r="P64" s="5" t="n"/>
       <c r="Q64" s="5" t="inlineStr">
         <is>
           <t>D0=257.77; 最新=2026-06-01; 相对D0=14.19%</t>
@@ -4912,24 +3958,12 @@
       <c r="J65" s="5" t="n">
         <v>160.5414</v>
       </c>
-      <c r="K65" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L65" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M65" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N65" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O65" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P65" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K65" s="5" t="n"/>
+      <c r="L65" s="5" t="n"/>
+      <c r="M65" s="5" t="n"/>
+      <c r="N65" s="5" t="n"/>
+      <c r="O65" s="5" t="n"/>
+      <c r="P65" s="5" t="n"/>
       <c r="Q65" s="5" t="inlineStr">
         <is>
           <t>D0=143.34; 最新=2026-06-01; 相对D0=12.00%</t>
@@ -4981,24 +4015,12 @@
       <c r="J66" s="5" t="n">
         <v>274.2531</v>
       </c>
-      <c r="K66" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L66" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M66" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N66" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O66" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P66" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K66" s="5" t="n"/>
+      <c r="L66" s="5" t="n"/>
+      <c r="M66" s="5" t="n"/>
+      <c r="N66" s="5" t="n"/>
+      <c r="O66" s="5" t="n"/>
+      <c r="P66" s="5" t="n"/>
       <c r="Q66" s="5" t="inlineStr">
         <is>
           <t>D0=259.21; 最新=2026-06-01; 相对D0=5.80%</t>
@@ -5050,24 +4072,12 @@
       <c r="J67" s="5" t="n">
         <v>270.67</v>
       </c>
-      <c r="K67" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L67" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M67" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N67" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O67" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P67" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K67" s="5" t="n"/>
+      <c r="L67" s="5" t="n"/>
+      <c r="M67" s="5" t="n"/>
+      <c r="N67" s="5" t="n"/>
+      <c r="O67" s="5" t="n"/>
+      <c r="P67" s="5" t="n"/>
       <c r="Q67" s="5" t="inlineStr">
         <is>
           <t>D0=287.75; 最新=2026-06-01; 相对D0=-5.94%</t>
@@ -5304,24 +4314,12 @@
       <c r="J79" s="5" t="n">
         <v>164.25</v>
       </c>
-      <c r="K79" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L79" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M79" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N79" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O79" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P79" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K79" s="5" t="n"/>
+      <c r="L79" s="5" t="n"/>
+      <c r="M79" s="5" t="n"/>
+      <c r="N79" s="5" t="n"/>
+      <c r="O79" s="5" t="n"/>
+      <c r="P79" s="5" t="n"/>
       <c r="Q79" s="5" t="inlineStr">
         <is>
           <t>D0=171.66; 最新=2026-06-01; 相对D0=-4.32%; 本次触发=2026-06-01(正式卖出); 历史重复1次; 重复日期=2026-06-01</t>
@@ -5373,24 +4371,6 @@
       <c r="J80" t="n">
         <v>102.3999</v>
       </c>
-      <c r="K80" t="n">
-        <v/>
-      </c>
-      <c r="L80" t="n">
-        <v/>
-      </c>
-      <c r="M80" t="n">
-        <v/>
-      </c>
-      <c r="N80" t="n">
-        <v/>
-      </c>
-      <c r="O80" t="n">
-        <v/>
-      </c>
-      <c r="P80" t="n">
-        <v/>
-      </c>
       <c r="Q80" t="inlineStr">
         <is>
           <t>D0=102.40; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式卖出)</t>
@@ -5442,24 +4422,6 @@
       <c r="J81" t="n">
         <v>65.2002</v>
       </c>
-      <c r="K81" t="n">
-        <v/>
-      </c>
-      <c r="L81" t="n">
-        <v/>
-      </c>
-      <c r="M81" t="n">
-        <v/>
-      </c>
-      <c r="N81" t="n">
-        <v/>
-      </c>
-      <c r="O81" t="n">
-        <v/>
-      </c>
-      <c r="P81" t="n">
-        <v/>
-      </c>
       <c r="Q81" t="inlineStr">
         <is>
           <t>D0=65.20; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式卖出)</t>
@@ -5511,24 +4473,12 @@
       <c r="J82" s="5" t="n">
         <v>137.035</v>
       </c>
-      <c r="K82" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L82" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M82" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N82" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O82" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P82" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K82" s="5" t="n"/>
+      <c r="L82" s="5" t="n"/>
+      <c r="M82" s="5" t="n"/>
+      <c r="N82" s="5" t="n"/>
+      <c r="O82" s="5" t="n"/>
+      <c r="P82" s="5" t="n"/>
       <c r="Q82" s="5" t="inlineStr">
         <is>
           <t>D0=137.03; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式卖出 | 预警卖出)</t>
@@ -5580,24 +4530,12 @@
       <c r="J83" s="5" t="n">
         <v>612.915</v>
       </c>
-      <c r="K83" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L83" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M83" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N83" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O83" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P83" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K83" s="5" t="n"/>
+      <c r="L83" s="5" t="n"/>
+      <c r="M83" s="5" t="n"/>
+      <c r="N83" s="5" t="n"/>
+      <c r="O83" s="5" t="n"/>
+      <c r="P83" s="5" t="n"/>
       <c r="Q83" s="5" t="inlineStr">
         <is>
           <t>D0=612.91; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式卖出 | 预警卖出)</t>
@@ -5649,24 +4587,12 @@
       <c r="J84" s="5" t="n">
         <v>24.485</v>
       </c>
-      <c r="K84" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L84" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M84" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N84" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O84" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P84" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K84" s="5" t="n"/>
+      <c r="L84" s="5" t="n"/>
+      <c r="M84" s="5" t="n"/>
+      <c r="N84" s="5" t="n"/>
+      <c r="O84" s="5" t="n"/>
+      <c r="P84" s="5" t="n"/>
       <c r="Q84" s="5" t="inlineStr">
         <is>
           <t>D0=24.48; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式卖出)</t>
@@ -5718,24 +4644,12 @@
       <c r="J85" s="5" t="n">
         <v>419.575</v>
       </c>
-      <c r="K85" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L85" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M85" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N85" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O85" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P85" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K85" s="5" t="n"/>
+      <c r="L85" s="5" t="n"/>
+      <c r="M85" s="5" t="n"/>
+      <c r="N85" s="5" t="n"/>
+      <c r="O85" s="5" t="n"/>
+      <c r="P85" s="5" t="n"/>
       <c r="Q85" s="5" t="inlineStr">
         <is>
           <t>D0=419.57; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式卖出 | 预警卖出)</t>
@@ -5787,24 +4701,12 @@
       <c r="J86" s="5" t="n">
         <v>39.505</v>
       </c>
-      <c r="K86" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L86" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M86" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N86" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O86" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P86" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K86" s="5" t="n"/>
+      <c r="L86" s="5" t="n"/>
+      <c r="M86" s="5" t="n"/>
+      <c r="N86" s="5" t="n"/>
+      <c r="O86" s="5" t="n"/>
+      <c r="P86" s="5" t="n"/>
       <c r="Q86" s="5" t="inlineStr">
         <is>
           <t>D0=41.47; 最新=2026-06-01; 相对D0=-4.74%</t>
@@ -5856,24 +4758,6 @@
       <c r="J87" t="n">
         <v>90.41</v>
       </c>
-      <c r="K87" t="n">
-        <v/>
-      </c>
-      <c r="L87" t="n">
-        <v/>
-      </c>
-      <c r="M87" t="n">
-        <v/>
-      </c>
-      <c r="N87" t="n">
-        <v/>
-      </c>
-      <c r="O87" t="n">
-        <v/>
-      </c>
-      <c r="P87" t="n">
-        <v/>
-      </c>
       <c r="Q87" t="inlineStr">
         <is>
           <t>D0=90.64; 最新=2026-06-01; 相对D0=-0.25%</t>
@@ -5925,24 +4809,12 @@
       <c r="J88" s="5" t="n">
         <v>186.6601</v>
       </c>
-      <c r="K88" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L88" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M88" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N88" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O88" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P88" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K88" s="5" t="n"/>
+      <c r="L88" s="5" t="n"/>
+      <c r="M88" s="5" t="n"/>
+      <c r="N88" s="5" t="n"/>
+      <c r="O88" s="5" t="n"/>
+      <c r="P88" s="5" t="n"/>
       <c r="Q88" s="5" t="inlineStr">
         <is>
           <t>D0=184.71; 最新=2026-06-01; 相对D0=1.06%</t>
@@ -5994,24 +4866,12 @@
       <c r="J89" s="5" t="n">
         <v>136.995</v>
       </c>
-      <c r="K89" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L89" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M89" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N89" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O89" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P89" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K89" s="5" t="n"/>
+      <c r="L89" s="5" t="n"/>
+      <c r="M89" s="5" t="n"/>
+      <c r="N89" s="5" t="n"/>
+      <c r="O89" s="5" t="n"/>
+      <c r="P89" s="5" t="n"/>
       <c r="Q89" s="5" t="inlineStr">
         <is>
           <t>D0=136.20; 最新=2026-06-01; 相对D0=0.58%</t>
@@ -6063,24 +4923,6 @@
       <c r="J90" t="n">
         <v>39.4</v>
       </c>
-      <c r="K90" t="n">
-        <v/>
-      </c>
-      <c r="L90" t="n">
-        <v/>
-      </c>
-      <c r="M90" t="n">
-        <v/>
-      </c>
-      <c r="N90" t="n">
-        <v/>
-      </c>
-      <c r="O90" t="n">
-        <v/>
-      </c>
-      <c r="P90" t="n">
-        <v/>
-      </c>
       <c r="Q90" t="inlineStr">
         <is>
           <t>D0=37.61; 最新=2026-06-01; 相对D0=4.76%</t>
@@ -6132,24 +4974,6 @@
       <c r="J91" t="n">
         <v>395.52</v>
       </c>
-      <c r="K91" t="n">
-        <v/>
-      </c>
-      <c r="L91" t="n">
-        <v/>
-      </c>
-      <c r="M91" t="n">
-        <v/>
-      </c>
-      <c r="N91" t="n">
-        <v/>
-      </c>
-      <c r="O91" t="n">
-        <v/>
-      </c>
-      <c r="P91" t="n">
-        <v/>
-      </c>
       <c r="Q91" t="inlineStr">
         <is>
           <t>D0=307.35; 最新=2026-06-01; 相对D0=28.69%</t>
@@ -6201,24 +5025,12 @@
       <c r="J92" s="5" t="n">
         <v>59.465</v>
       </c>
-      <c r="K92" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L92" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M92" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N92" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O92" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P92" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K92" s="5" t="n"/>
+      <c r="L92" s="5" t="n"/>
+      <c r="M92" s="5" t="n"/>
+      <c r="N92" s="5" t="n"/>
+      <c r="O92" s="5" t="n"/>
+      <c r="P92" s="5" t="n"/>
       <c r="Q92" s="5" t="inlineStr">
         <is>
           <t>D0=57.46; 最新=2026-06-01; 相对D0=3.49%</t>
@@ -6270,24 +5082,12 @@
       <c r="J93" s="5" t="n">
         <v>13.875</v>
       </c>
-      <c r="K93" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L93" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M93" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N93" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O93" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P93" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K93" s="5" t="n"/>
+      <c r="L93" s="5" t="n"/>
+      <c r="M93" s="5" t="n"/>
+      <c r="N93" s="5" t="n"/>
+      <c r="O93" s="5" t="n"/>
+      <c r="P93" s="5" t="n"/>
       <c r="Q93" s="5" t="inlineStr">
         <is>
           <t>D0=13.35; 最新=2026-06-01; 相对D0=3.93%</t>
@@ -6339,24 +5139,12 @@
       <c r="J94" s="5" t="n">
         <v>54.7999</v>
       </c>
-      <c r="K94" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L94" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M94" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N94" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O94" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P94" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K94" s="5" t="n"/>
+      <c r="L94" s="5" t="n"/>
+      <c r="M94" s="5" t="n"/>
+      <c r="N94" s="5" t="n"/>
+      <c r="O94" s="5" t="n"/>
+      <c r="P94" s="5" t="n"/>
       <c r="Q94" s="5" t="inlineStr">
         <is>
           <t>D0=56.50; 最新=2026-06-01; 相对D0=-3.01%</t>
@@ -6408,24 +5196,6 @@
       <c r="J95" t="n">
         <v>154.22</v>
       </c>
-      <c r="K95" t="n">
-        <v/>
-      </c>
-      <c r="L95" t="n">
-        <v/>
-      </c>
-      <c r="M95" t="n">
-        <v/>
-      </c>
-      <c r="N95" t="n">
-        <v/>
-      </c>
-      <c r="O95" t="n">
-        <v/>
-      </c>
-      <c r="P95" t="n">
-        <v/>
-      </c>
       <c r="Q95" t="inlineStr">
         <is>
           <t>D0=126.41; 最新=2026-06-01; 相对D0=22.00%</t>
@@ -6477,24 +5247,12 @@
       <c r="J96" s="5" t="n">
         <v>108.772</v>
       </c>
-      <c r="K96" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L96" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M96" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N96" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O96" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P96" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K96" s="5" t="n"/>
+      <c r="L96" s="5" t="n"/>
+      <c r="M96" s="5" t="n"/>
+      <c r="N96" s="5" t="n"/>
+      <c r="O96" s="5" t="n"/>
+      <c r="P96" s="5" t="n"/>
       <c r="Q96" s="5" t="inlineStr">
         <is>
           <t>D0=115.70; 最新=2026-06-01; 相对D0=-5.99%</t>
@@ -6546,24 +5304,6 @@
       <c r="J97" t="n">
         <v>270.755</v>
       </c>
-      <c r="K97" t="n">
-        <v/>
-      </c>
-      <c r="L97" t="n">
-        <v/>
-      </c>
-      <c r="M97" t="n">
-        <v/>
-      </c>
-      <c r="N97" t="n">
-        <v/>
-      </c>
-      <c r="O97" t="n">
-        <v/>
-      </c>
-      <c r="P97" t="n">
-        <v/>
-      </c>
       <c r="Q97" t="inlineStr">
         <is>
           <t>D0=286.31; 最新=2026-06-01; 相对D0=-5.43%</t>
@@ -6615,24 +5355,12 @@
       <c r="J98" s="5" t="n">
         <v>175.4463</v>
       </c>
-      <c r="K98" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L98" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M98" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N98" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O98" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P98" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K98" s="5" t="n"/>
+      <c r="L98" s="5" t="n"/>
+      <c r="M98" s="5" t="n"/>
+      <c r="N98" s="5" t="n"/>
+      <c r="O98" s="5" t="n"/>
+      <c r="P98" s="5" t="n"/>
       <c r="Q98" s="5" t="inlineStr">
         <is>
           <t>D0=182.97; 最新=2026-06-01; 相对D0=-4.11%</t>
@@ -6684,24 +5412,6 @@
       <c r="J99" t="n">
         <v>482.17</v>
       </c>
-      <c r="K99" t="n">
-        <v/>
-      </c>
-      <c r="L99" t="n">
-        <v/>
-      </c>
-      <c r="M99" t="n">
-        <v/>
-      </c>
-      <c r="N99" t="n">
-        <v/>
-      </c>
-      <c r="O99" t="n">
-        <v/>
-      </c>
-      <c r="P99" t="n">
-        <v/>
-      </c>
       <c r="Q99" t="inlineStr">
         <is>
           <t>D0=480.64; 最新=2026-06-01; 相对D0=0.32%</t>
@@ -6753,24 +5463,12 @@
       <c r="J100" s="5" t="n">
         <v>90.36499999999999</v>
       </c>
-      <c r="K100" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L100" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M100" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N100" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O100" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P100" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K100" s="5" t="n"/>
+      <c r="L100" s="5" t="n"/>
+      <c r="M100" s="5" t="n"/>
+      <c r="N100" s="5" t="n"/>
+      <c r="O100" s="5" t="n"/>
+      <c r="P100" s="5" t="n"/>
       <c r="Q100" s="5" t="inlineStr">
         <is>
           <t>D0=92.33; 最新=2026-06-01; 相对D0=-2.13%</t>
@@ -6822,24 +5520,12 @@
       <c r="J101" s="5" t="n">
         <v>70.755</v>
       </c>
-      <c r="K101" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L101" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M101" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N101" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O101" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P101" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K101" s="5" t="n"/>
+      <c r="L101" s="5" t="n"/>
+      <c r="M101" s="5" t="n"/>
+      <c r="N101" s="5" t="n"/>
+      <c r="O101" s="5" t="n"/>
+      <c r="P101" s="5" t="n"/>
       <c r="Q101" s="5" t="inlineStr">
         <is>
           <t>D0=69.56; 最新=2026-06-01; 相对D0=1.72%</t>
@@ -6891,24 +5577,6 @@
       <c r="J102" t="n">
         <v>274.81</v>
       </c>
-      <c r="K102" t="n">
-        <v/>
-      </c>
-      <c r="L102" t="n">
-        <v/>
-      </c>
-      <c r="M102" t="n">
-        <v/>
-      </c>
-      <c r="N102" t="n">
-        <v/>
-      </c>
-      <c r="O102" t="n">
-        <v/>
-      </c>
-      <c r="P102" t="n">
-        <v/>
-      </c>
       <c r="Q102" t="inlineStr">
         <is>
           <t>D0=285.00; 最新=2026-06-01; 相对D0=-3.58%</t>
@@ -6960,24 +5628,12 @@
       <c r="J103" s="5" t="n">
         <v>355.64</v>
       </c>
-      <c r="K103" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L103" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M103" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N103" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O103" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P103" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K103" s="5" t="n"/>
+      <c r="L103" s="5" t="n"/>
+      <c r="M103" s="5" t="n"/>
+      <c r="N103" s="5" t="n"/>
+      <c r="O103" s="5" t="n"/>
+      <c r="P103" s="5" t="n"/>
       <c r="Q103" s="5" t="inlineStr">
         <is>
           <t>D0=361.47; 最新=2026-06-01; 相对D0=-1.61%</t>
@@ -7029,24 +5685,6 @@
       <c r="J104" t="n">
         <v>26.166</v>
       </c>
-      <c r="K104" t="n">
-        <v/>
-      </c>
-      <c r="L104" t="n">
-        <v/>
-      </c>
-      <c r="M104" t="n">
-        <v/>
-      </c>
-      <c r="N104" t="n">
-        <v/>
-      </c>
-      <c r="O104" t="n">
-        <v/>
-      </c>
-      <c r="P104" t="n">
-        <v/>
-      </c>
       <c r="Q104" t="inlineStr">
         <is>
           <t>D0=18.88; 最新=2026-06-01; 相对D0=38.59%</t>
@@ -7098,24 +5736,6 @@
       <c r="J105" t="n">
         <v>110.74</v>
       </c>
-      <c r="K105" t="n">
-        <v/>
-      </c>
-      <c r="L105" t="n">
-        <v/>
-      </c>
-      <c r="M105" t="n">
-        <v/>
-      </c>
-      <c r="N105" t="n">
-        <v/>
-      </c>
-      <c r="O105" t="n">
-        <v/>
-      </c>
-      <c r="P105" t="n">
-        <v/>
-      </c>
       <c r="Q105" t="inlineStr">
         <is>
           <t>D0=114.68; 最新=2026-06-01; 相对D0=-3.44%</t>
@@ -7167,24 +5787,6 @@
       <c r="J106" t="n">
         <v>130.83</v>
       </c>
-      <c r="K106" t="n">
-        <v/>
-      </c>
-      <c r="L106" t="n">
-        <v/>
-      </c>
-      <c r="M106" t="n">
-        <v/>
-      </c>
-      <c r="N106" t="n">
-        <v/>
-      </c>
-      <c r="O106" t="n">
-        <v/>
-      </c>
-      <c r="P106" t="n">
-        <v/>
-      </c>
       <c r="Q106" t="inlineStr">
         <is>
           <t>D0=134.08; 最新=2026-06-01; 相对D0=-2.42%</t>
@@ -7236,24 +5838,12 @@
       <c r="J107" s="5" t="n">
         <v>243.92</v>
       </c>
-      <c r="K107" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L107" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M107" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N107" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O107" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P107" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K107" s="5" t="n"/>
+      <c r="L107" s="5" t="n"/>
+      <c r="M107" s="5" t="n"/>
+      <c r="N107" s="5" t="n"/>
+      <c r="O107" s="5" t="n"/>
+      <c r="P107" s="5" t="n"/>
       <c r="Q107" s="5" t="inlineStr">
         <is>
           <t>D0=255.23; 最新=2026-06-01; 相对D0=-4.43%</t>
@@ -7350,7 +5940,6 @@
         <v>2</v>
       </c>
     </row>
-    <row r="116"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7362,7 +5951,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L29"/>
+  <dimension ref="A1:L25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -7975,10 +6564,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7990,7 +6575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J37"/>
+  <dimension ref="A1:J34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -8328,7 +6913,6 @@
       <c r="I9" s="13" t="n">
         <v>0.077028</v>
       </c>
-      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -8366,7 +6950,6 @@
       <c r="I10" s="13" t="n">
         <v>0.201644</v>
       </c>
-      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -8848,9 +7431,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8862,7 +7442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -8942,7 +7522,7 @@
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>买入跟踪 | 正式买入 | 第一买入点 | 预警买入</t>
+          <t>买入跟踪 | 正式买入 | 第一观察点 | 预警买入</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -9396,7 +7976,6 @@
       <c r="G22" s="12" t="n">
         <v>-0.024239</v>
       </c>
-      <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
@@ -9520,7 +8099,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9532,7 +8110,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -9892,7 +8470,6 @@
       <c r="E14" t="n">
         <v>154.305</v>
       </c>
-      <c r="F14" t="inlineStr"/>
     </row>
     <row r="15"/>
     <row r="16">
@@ -10270,7 +8847,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11260,8 +9836,6 @@
       <c r="T11" t="b">
         <v>0</v>
       </c>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr">
         <is>
           <t>4H 0出; 4H_RSI=45.21; 4H分金=54.29</t>
@@ -11543,7 +10117,6 @@
           <t>DXY</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>98 TradingView导入</t>
@@ -11626,7 +10199,6 @@
           <t>DXY</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>98 TradingView导入</t>
@@ -12855,7 +11427,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -13075,8 +11647,6 @@
       <c r="T32" t="b">
         <v>0</v>
       </c>
-      <c r="U32" t="inlineStr"/>
-      <c r="V32" t="inlineStr"/>
       <c r="W32" t="inlineStr">
         <is>
           <t>4H 0出; 4H_RSI=46.96; 4H分金=50.55</t>
@@ -13158,8 +11728,6 @@
       <c r="T33" t="b">
         <v>0</v>
       </c>
-      <c r="U33" t="inlineStr"/>
-      <c r="V33" t="inlineStr"/>
       <c r="W33" t="inlineStr">
         <is>
           <t>4H 0出; 4H_RSI=43.16; 4H分金=49.44</t>
@@ -14546,8 +13114,6 @@
       <c r="T49" t="b">
         <v>0</v>
       </c>
-      <c r="U49" t="inlineStr"/>
-      <c r="V49" t="inlineStr"/>
       <c r="W49" t="inlineStr">
         <is>
           <t>4H 0出; 4H_RSI=47.16; 4H分金=56.15</t>
@@ -14568,7 +13134,6 @@
           <t>VIX</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
           <t>98 TradingView导入</t>
@@ -14625,8 +13190,6 @@
       <c r="T50" t="b">
         <v>0</v>
       </c>
-      <c r="U50" t="inlineStr"/>
-      <c r="V50" t="inlineStr"/>
       <c r="W50" t="inlineStr">
         <is>
           <t>4H 0出; 4H_RSI=44.44; 4H分金=52.29</t>
@@ -15046,7 +13609,6 @@
       <c r="D2" s="8" t="n">
         <v>46170</v>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" s="8" t="n">
         <v>46170</v>
       </c>
@@ -15095,7 +13657,6 @@
           <t>98 超巨</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" s="8" t="n">
         <v>46168</v>
       </c>
@@ -15150,7 +13711,6 @@
       <c r="D4" s="8" t="n">
         <v>46164</v>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" s="8" t="n">
         <v>46164</v>
       </c>
@@ -15256,7 +13816,6 @@
       <c r="D6" s="8" t="n">
         <v>46170</v>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" s="8" t="n">
         <v>46170</v>
       </c>
@@ -15915,7 +14474,6 @@
       <c r="I9" t="n">
         <v>2</v>
       </c>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" s="8" t="n">
         <v>46171</v>
       </c>
@@ -16027,7 +14585,6 @@
       <c r="I11" t="n">
         <v>4</v>
       </c>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" s="8" t="n">
         <v>46169</v>
       </c>
@@ -16116,7 +14673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P42"/>
+  <dimension ref="A1:P37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -17056,7 +15613,6 @@
       <c r="O16" s="13" t="n">
         <v>0.07771599999999999</v>
       </c>
-      <c r="P16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -17112,7 +15668,6 @@
       <c r="O17" s="13" t="n">
         <v>0.103908</v>
       </c>
-      <c r="P17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -17288,7 +15843,6 @@
       <c r="O20" s="12" t="n">
         <v>-0.014882</v>
       </c>
-      <c r="P20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -17624,11 +16178,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -17640,7 +16189,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q42"/>
+  <dimension ref="A1:Q37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -17801,24 +16350,12 @@
       <c r="J3" s="5" t="n">
         <v>181.49</v>
       </c>
-      <c r="K3" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L3" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M3" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N3" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O3" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P3" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K3" s="5" t="n"/>
+      <c r="L3" s="5" t="n"/>
+      <c r="M3" s="5" t="n"/>
+      <c r="N3" s="5" t="n"/>
+      <c r="O3" s="5" t="n"/>
+      <c r="P3" s="5" t="n"/>
       <c r="Q3" s="5" t="inlineStr">
         <is>
           <t>D0=181.49; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -17870,24 +16407,12 @@
       <c r="J4" s="5" t="n">
         <v>202.91</v>
       </c>
-      <c r="K4" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L4" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M4" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N4" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O4" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P4" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K4" s="5" t="n"/>
+      <c r="L4" s="5" t="n"/>
+      <c r="M4" s="5" t="n"/>
+      <c r="N4" s="5" t="n"/>
+      <c r="O4" s="5" t="n"/>
+      <c r="P4" s="5" t="n"/>
       <c r="Q4" s="5" t="inlineStr">
         <is>
           <t>D0=202.91; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -17939,24 +16464,12 @@
       <c r="J5" s="5" t="n">
         <v>167.37</v>
       </c>
-      <c r="K5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P5" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K5" s="5" t="n"/>
+      <c r="L5" s="5" t="n"/>
+      <c r="M5" s="5" t="n"/>
+      <c r="N5" s="5" t="n"/>
+      <c r="O5" s="5" t="n"/>
+      <c r="P5" s="5" t="n"/>
       <c r="Q5" s="5" t="inlineStr">
         <is>
           <t>D0=167.37; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -18008,24 +16521,12 @@
       <c r="J6" s="5" t="n">
         <v>46.53</v>
       </c>
-      <c r="K6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P6" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K6" s="5" t="n"/>
+      <c r="L6" s="5" t="n"/>
+      <c r="M6" s="5" t="n"/>
+      <c r="N6" s="5" t="n"/>
+      <c r="O6" s="5" t="n"/>
+      <c r="P6" s="5" t="n"/>
       <c r="Q6" s="5" t="inlineStr">
         <is>
           <t>D0=46.53; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -18077,24 +16578,6 @@
       <c r="J7" t="n">
         <v>16.12</v>
       </c>
-      <c r="K7" t="n">
-        <v/>
-      </c>
-      <c r="L7" t="n">
-        <v/>
-      </c>
-      <c r="M7" t="n">
-        <v/>
-      </c>
-      <c r="N7" t="n">
-        <v/>
-      </c>
-      <c r="O7" t="n">
-        <v/>
-      </c>
-      <c r="P7" t="n">
-        <v/>
-      </c>
       <c r="Q7" t="inlineStr">
         <is>
           <t>D0=16.12; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -18146,24 +16629,12 @@
       <c r="J8" s="5" t="n">
         <v>180.07</v>
       </c>
-      <c r="K8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P8" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K8" s="5" t="n"/>
+      <c r="L8" s="5" t="n"/>
+      <c r="M8" s="5" t="n"/>
+      <c r="N8" s="5" t="n"/>
+      <c r="O8" s="5" t="n"/>
+      <c r="P8" s="5" t="n"/>
       <c r="Q8" s="5" t="inlineStr">
         <is>
           <t>D0=180.07; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -18215,24 +16686,12 @@
       <c r="J9" s="5" t="n">
         <v>48.12</v>
       </c>
-      <c r="K9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P9" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K9" s="5" t="n"/>
+      <c r="L9" s="5" t="n"/>
+      <c r="M9" s="5" t="n"/>
+      <c r="N9" s="5" t="n"/>
+      <c r="O9" s="5" t="n"/>
+      <c r="P9" s="5" t="n"/>
       <c r="Q9" s="5" t="inlineStr">
         <is>
           <t>D0=48.12; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -18284,24 +16743,6 @@
       <c r="J10" t="n">
         <v>141.22</v>
       </c>
-      <c r="K10" t="n">
-        <v/>
-      </c>
-      <c r="L10" t="n">
-        <v/>
-      </c>
-      <c r="M10" t="n">
-        <v/>
-      </c>
-      <c r="N10" t="n">
-        <v/>
-      </c>
-      <c r="O10" t="n">
-        <v/>
-      </c>
-      <c r="P10" t="n">
-        <v/>
-      </c>
       <c r="Q10" t="inlineStr">
         <is>
           <t>D0=141.22; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -18353,24 +16794,12 @@
       <c r="J11" s="5" t="n">
         <v>391.35</v>
       </c>
-      <c r="K11" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L11" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M11" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N11" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O11" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P11" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K11" s="5" t="n"/>
+      <c r="L11" s="5" t="n"/>
+      <c r="M11" s="5" t="n"/>
+      <c r="N11" s="5" t="n"/>
+      <c r="O11" s="5" t="n"/>
+      <c r="P11" s="5" t="n"/>
       <c r="Q11" s="5" t="inlineStr">
         <is>
           <t>D0=391.35; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -18422,24 +16851,12 @@
       <c r="J12" s="5" t="n">
         <v>1038.74</v>
       </c>
-      <c r="K12" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L12" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M12" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N12" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O12" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P12" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K12" s="5" t="n"/>
+      <c r="L12" s="5" t="n"/>
+      <c r="M12" s="5" t="n"/>
+      <c r="N12" s="5" t="n"/>
+      <c r="O12" s="5" t="n"/>
+      <c r="P12" s="5" t="n"/>
       <c r="Q12" s="5" t="inlineStr">
         <is>
           <t>D0=1038.74; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -18491,24 +16908,12 @@
       <c r="J13" s="5" t="n">
         <v>179.36</v>
       </c>
-      <c r="K13" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L13" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M13" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N13" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O13" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P13" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K13" s="5" t="n"/>
+      <c r="L13" s="5" t="n"/>
+      <c r="M13" s="5" t="n"/>
+      <c r="N13" s="5" t="n"/>
+      <c r="O13" s="5" t="n"/>
+      <c r="P13" s="5" t="n"/>
       <c r="Q13" s="5" t="inlineStr">
         <is>
           <t>D0=179.36; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -18560,24 +16965,12 @@
       <c r="J14" s="5" t="n">
         <v>326.13</v>
       </c>
-      <c r="K14" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L14" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M14" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N14" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O14" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P14" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K14" s="5" t="n"/>
+      <c r="L14" s="5" t="n"/>
+      <c r="M14" s="5" t="n"/>
+      <c r="N14" s="5" t="n"/>
+      <c r="O14" s="5" t="n"/>
+      <c r="P14" s="5" t="n"/>
       <c r="Q14" s="5" t="inlineStr">
         <is>
           <t>D0=326.13; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -18629,24 +17022,6 @@
       <c r="J15" t="n">
         <v>22.51</v>
       </c>
-      <c r="K15" t="n">
-        <v/>
-      </c>
-      <c r="L15" t="n">
-        <v/>
-      </c>
-      <c r="M15" t="n">
-        <v/>
-      </c>
-      <c r="N15" t="n">
-        <v/>
-      </c>
-      <c r="O15" t="n">
-        <v/>
-      </c>
-      <c r="P15" t="n">
-        <v/>
-      </c>
       <c r="Q15" t="inlineStr">
         <is>
           <t>D0=22.51; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -18698,24 +17073,6 @@
       <c r="J16" t="n">
         <v>232</v>
       </c>
-      <c r="K16" t="n">
-        <v/>
-      </c>
-      <c r="L16" t="n">
-        <v/>
-      </c>
-      <c r="M16" t="n">
-        <v/>
-      </c>
-      <c r="N16" t="n">
-        <v/>
-      </c>
-      <c r="O16" t="n">
-        <v/>
-      </c>
-      <c r="P16" t="n">
-        <v/>
-      </c>
       <c r="Q16" t="inlineStr">
         <is>
           <t>D0=232.00; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -18767,24 +17124,6 @@
       <c r="J17" t="n">
         <v>130.5</v>
       </c>
-      <c r="K17" t="n">
-        <v/>
-      </c>
-      <c r="L17" t="n">
-        <v/>
-      </c>
-      <c r="M17" t="n">
-        <v/>
-      </c>
-      <c r="N17" t="n">
-        <v/>
-      </c>
-      <c r="O17" t="n">
-        <v/>
-      </c>
-      <c r="P17" t="n">
-        <v/>
-      </c>
       <c r="Q17" t="inlineStr">
         <is>
           <t>D0=130.50; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -18836,24 +17175,12 @@
       <c r="J18" s="5" t="n">
         <v>262.25</v>
       </c>
-      <c r="K18" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L18" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M18" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N18" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O18" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P18" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K18" s="5" t="n"/>
+      <c r="L18" s="5" t="n"/>
+      <c r="M18" s="5" t="n"/>
+      <c r="N18" s="5" t="n"/>
+      <c r="O18" s="5" t="n"/>
+      <c r="P18" s="5" t="n"/>
       <c r="Q18" s="5" t="inlineStr">
         <is>
           <t>D0=262.25; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -18905,24 +17232,12 @@
       <c r="J19" s="5" t="n">
         <v>85.42</v>
       </c>
-      <c r="K19" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L19" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M19" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N19" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O19" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P19" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K19" s="5" t="n"/>
+      <c r="L19" s="5" t="n"/>
+      <c r="M19" s="5" t="n"/>
+      <c r="N19" s="5" t="n"/>
+      <c r="O19" s="5" t="n"/>
+      <c r="P19" s="5" t="n"/>
       <c r="Q19" s="5" t="inlineStr">
         <is>
           <t>D0=85.42; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -18974,24 +17289,6 @@
       <c r="J20" t="n">
         <v>426.01</v>
       </c>
-      <c r="K20" t="n">
-        <v/>
-      </c>
-      <c r="L20" t="n">
-        <v/>
-      </c>
-      <c r="M20" t="n">
-        <v/>
-      </c>
-      <c r="N20" t="n">
-        <v/>
-      </c>
-      <c r="O20" t="n">
-        <v/>
-      </c>
-      <c r="P20" t="n">
-        <v/>
-      </c>
       <c r="Q20" t="inlineStr">
         <is>
           <t>D0=426.01; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -19043,24 +17340,12 @@
       <c r="J21" s="5" t="n">
         <v>13.02</v>
       </c>
-      <c r="K21" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L21" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M21" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N21" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O21" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P21" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K21" s="5" t="n"/>
+      <c r="L21" s="5" t="n"/>
+      <c r="M21" s="5" t="n"/>
+      <c r="N21" s="5" t="n"/>
+      <c r="O21" s="5" t="n"/>
+      <c r="P21" s="5" t="n"/>
       <c r="Q21" s="5" t="inlineStr">
         <is>
           <t>D0=13.02; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -19297,24 +17582,12 @@
       <c r="J33" s="5" t="n">
         <v>41.47</v>
       </c>
-      <c r="K33" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L33" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M33" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N33" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O33" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P33" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K33" s="5" t="n"/>
+      <c r="L33" s="5" t="n"/>
+      <c r="M33" s="5" t="n"/>
+      <c r="N33" s="5" t="n"/>
+      <c r="O33" s="5" t="n"/>
+      <c r="P33" s="5" t="n"/>
       <c r="Q33" s="5" t="inlineStr">
         <is>
           <t>D0=41.47; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -19359,11 +17632,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -19375,7 +17643,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N44"/>
+  <dimension ref="A1:N43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -19575,7 +17843,6 @@
       <c r="M4" s="13" t="n">
         <v>0.09560200000000001</v>
       </c>
-      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -19965,7 +18232,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>买入跟踪 | 第一买入点</t>
+          <t>买入跟踪 | 第一观察点</t>
         </is>
       </c>
       <c r="E12" s="5" t="n">
@@ -20069,7 +18336,7 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>买入跟踪 | 第一买入点</t>
+          <t>买入跟踪 | 第一观察点</t>
         </is>
       </c>
       <c r="E14" s="5" t="n">
@@ -20149,7 +18416,6 @@
       <c r="M15" s="13" t="n">
         <v>0.00189</v>
       </c>
-      <c r="N15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -20253,7 +18519,6 @@
       <c r="M17" s="12" t="n">
         <v>-0.012442</v>
       </c>
-      <c r="N17" t="inlineStr"/>
     </row>
     <row r="18"/>
     <row r="19">
@@ -20865,7 +19130,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
